--- a/examples/sequence/Cheeseboard/metadata.xlsx
+++ b/examples/sequence/Cheeseboard/metadata.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="0"/>
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="animal_day" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -16,49 +16,49 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
-    <t>animal</t>
+    <t>Animal</t>
   </si>
   <si>
-    <t>day</t>
+    <t>Day</t>
   </si>
   <si>
     <t>reward_ID</t>
   </si>
   <si>
-    <t>start_box</t>
-  </si>
-  <si>
-    <t>meters_per_pixel</t>
-  </si>
-  <si>
-    <t>reward_coordinates</t>
-  </si>
-  <si>
     <t>reward_type</t>
   </si>
   <si>
-    <t>start_box-392D1.csv</t>
+    <t>MetersPerPixel</t>
   </si>
   <si>
-    <t>meters_per_pixel-diagonal-0.1-392D1.csv</t>
+    <t>RewardPerimeter</t>
   </si>
   <si>
-    <t>reward-392D1.csv</t>
+    <t>StartPerimeter</t>
   </si>
   <si>
     <t>original</t>
   </si>
   <si>
-    <t>start_box-461R7.csv</t>
+    <t>392D1</t>
   </si>
   <si>
-    <t>meters_per_pixel-diagonal-0.1-461R7.csv</t>
+    <t>reward_392D1</t>
   </si>
   <si>
-    <t>reward-461R7.csv</t>
+    <t>start_392D1</t>
   </si>
   <si>
     <t>different</t>
+  </si>
+  <si>
+    <t>461R7</t>
+  </si>
+  <si>
+    <t>reward_461R7</t>
+  </si>
+  <si>
+    <t>start_461R7</t>
   </si>
 </sst>
 </file>
@@ -630,8 +630,8 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="21.28125"/>
-    <col customWidth="1" min="5" max="5" width="37.00390625"/>
+    <col customWidth="1" min="6" max="6" width="20.28125"/>
+    <col customWidth="1" min="7" max="7" width="17.7109375"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1556,7 +1556,7 @@
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
         <v>12</v>
@@ -1565,7 +1565,7 @@
         <v>13</v>
       </c>
       <c r="G44" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
@@ -1577,7 +1577,7 @@
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E45" t="s">
         <v>12</v>
@@ -1586,7 +1586,7 @@
         <v>13</v>
       </c>
       <c r="G45" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
@@ -1598,7 +1598,7 @@
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E46" t="s">
         <v>12</v>
@@ -1607,7 +1607,7 @@
         <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -1619,7 +1619,7 @@
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
         <v>12</v>
@@ -1628,7 +1628,7 @@
         <v>13</v>
       </c>
       <c r="G47" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
         <v>12</v>
@@ -1649,7 +1649,7 @@
         <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -1661,7 +1661,7 @@
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E49" t="s">
         <v>12</v>
@@ -1670,7 +1670,7 @@
         <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
@@ -1682,7 +1682,7 @@
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E50" t="s">
         <v>12</v>
@@ -1691,7 +1691,7 @@
         <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
@@ -1703,7 +1703,7 @@
         <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
@@ -1724,7 +1724,7 @@
         <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -1733,7 +1733,7 @@
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
@@ -1745,7 +1745,7 @@
         <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -1754,7 +1754,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
@@ -1766,7 +1766,7 @@
         <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -1775,7 +1775,7 @@
         <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
@@ -1787,7 +1787,7 @@
         <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -1796,7 +1796,7 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
@@ -1808,7 +1808,7 @@
         <v>116</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -1829,7 +1829,7 @@
         <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -1838,7 +1838,7 @@
         <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
@@ -2148,7 +2148,7 @@
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
         <v>12</v>
@@ -2157,7 +2157,7 @@
         <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73">
@@ -2169,7 +2169,7 @@
         <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E73" t="s">
         <v>12</v>
@@ -2178,7 +2178,7 @@
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -2190,7 +2190,7 @@
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E74" t="s">
         <v>12</v>
@@ -2199,7 +2199,7 @@
         <v>13</v>
       </c>
       <c r="G74" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
@@ -2211,7 +2211,7 @@
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
         <v>12</v>
@@ -2220,7 +2220,7 @@
         <v>13</v>
       </c>
       <c r="G75" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76">
@@ -2232,7 +2232,7 @@
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E76" t="s">
         <v>12</v>
@@ -2241,7 +2241,7 @@
         <v>13</v>
       </c>
       <c r="G76" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
@@ -2253,7 +2253,7 @@
         <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E77" t="s">
         <v>12</v>
@@ -2262,7 +2262,7 @@
         <v>13</v>
       </c>
       <c r="G77" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78">
@@ -2274,7 +2274,7 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E78" t="s">
         <v>12</v>
@@ -2283,7 +2283,7 @@
         <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79">
@@ -2295,7 +2295,7 @@
         <v>116</v>
       </c>
       <c r="D79" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -2304,7 +2304,7 @@
         <v>9</v>
       </c>
       <c r="G79" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -2316,7 +2316,7 @@
         <v>116</v>
       </c>
       <c r="D80" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -2325,7 +2325,7 @@
         <v>9</v>
       </c>
       <c r="G80" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
@@ -2337,7 +2337,7 @@
         <v>116</v>
       </c>
       <c r="D81" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -2346,7 +2346,7 @@
         <v>9</v>
       </c>
       <c r="G81" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
@@ -2358,7 +2358,7 @@
         <v>116</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -2367,7 +2367,7 @@
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -2379,7 +2379,7 @@
         <v>116</v>
       </c>
       <c r="D83" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -2388,7 +2388,7 @@
         <v>9</v>
       </c>
       <c r="G83" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
@@ -2400,7 +2400,7 @@
         <v>116</v>
       </c>
       <c r="D84" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -2409,7 +2409,7 @@
         <v>9</v>
       </c>
       <c r="G84" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -2421,7 +2421,7 @@
         <v>116</v>
       </c>
       <c r="D85" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
       <c r="G85" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
@@ -2444,7 +2444,7 @@
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E86" t="s">
         <v>12</v>
@@ -2453,7 +2453,7 @@
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
@@ -2465,7 +2465,7 @@
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E87" t="s">
         <v>12</v>
@@ -2474,7 +2474,7 @@
         <v>13</v>
       </c>
       <c r="G87" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88">
@@ -2486,7 +2486,7 @@
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
         <v>12</v>
@@ -2495,7 +2495,7 @@
         <v>13</v>
       </c>
       <c r="G88" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89">
@@ -2507,7 +2507,7 @@
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E89" t="s">
         <v>12</v>
@@ -2516,7 +2516,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90">
@@ -2528,7 +2528,7 @@
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E90" t="s">
         <v>12</v>
@@ -2537,7 +2537,7 @@
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91">
@@ -2549,7 +2549,7 @@
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E91" t="s">
         <v>12</v>
@@ -2558,7 +2558,7 @@
         <v>13</v>
       </c>
       <c r="G91" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92">
@@ -2570,7 +2570,7 @@
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E92" t="s">
         <v>12</v>
@@ -2579,7 +2579,7 @@
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93">
@@ -2591,7 +2591,7 @@
         <v>116</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -2600,7 +2600,7 @@
         <v>9</v>
       </c>
       <c r="G93" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
@@ -2612,7 +2612,7 @@
         <v>116</v>
       </c>
       <c r="D94" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -2621,7 +2621,7 @@
         <v>9</v>
       </c>
       <c r="G94" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
@@ -2633,7 +2633,7 @@
         <v>116</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -2642,7 +2642,7 @@
         <v>9</v>
       </c>
       <c r="G95" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
@@ -2654,7 +2654,7 @@
         <v>116</v>
       </c>
       <c r="D96" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -2663,7 +2663,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -2675,7 +2675,7 @@
         <v>116</v>
       </c>
       <c r="D97" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -2684,7 +2684,7 @@
         <v>9</v>
       </c>
       <c r="G97" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98">
@@ -2696,7 +2696,7 @@
         <v>116</v>
       </c>
       <c r="D98" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -2705,7 +2705,7 @@
         <v>9</v>
       </c>
       <c r="G98" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
@@ -2717,7 +2717,7 @@
         <v>116</v>
       </c>
       <c r="D99" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -2726,7 +2726,7 @@
         <v>9</v>
       </c>
       <c r="G99" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100">
@@ -2740,7 +2740,7 @@
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E100" t="s">
         <v>12</v>
@@ -2749,7 +2749,7 @@
         <v>13</v>
       </c>
       <c r="G100" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101">
@@ -2761,7 +2761,7 @@
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E101" t="s">
         <v>12</v>
@@ -2770,7 +2770,7 @@
         <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102">
@@ -2782,7 +2782,7 @@
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E102" t="s">
         <v>12</v>
@@ -2791,7 +2791,7 @@
         <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103">
@@ -2803,7 +2803,7 @@
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E103" t="s">
         <v>12</v>
@@ -2812,7 +2812,7 @@
         <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104">
@@ -2824,7 +2824,7 @@
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E104" t="s">
         <v>12</v>
@@ -2833,7 +2833,7 @@
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105">
@@ -2845,7 +2845,7 @@
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E105" t="s">
         <v>12</v>
@@ -2854,7 +2854,7 @@
         <v>13</v>
       </c>
       <c r="G105" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106">
@@ -2866,7 +2866,7 @@
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E106" t="s">
         <v>12</v>
@@ -2875,7 +2875,7 @@
         <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107">
@@ -2887,7 +2887,7 @@
         <v>116</v>
       </c>
       <c r="D107" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -2896,7 +2896,7 @@
         <v>9</v>
       </c>
       <c r="G107" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108">
@@ -2908,7 +2908,7 @@
         <v>116</v>
       </c>
       <c r="D108" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9</v>
       </c>
       <c r="G108" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109">
@@ -2929,7 +2929,7 @@
         <v>116</v>
       </c>
       <c r="D109" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -2938,7 +2938,7 @@
         <v>9</v>
       </c>
       <c r="G109" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110">
@@ -2950,7 +2950,7 @@
         <v>116</v>
       </c>
       <c r="D110" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -2959,7 +2959,7 @@
         <v>9</v>
       </c>
       <c r="G110" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111">
@@ -2971,7 +2971,7 @@
         <v>116</v>
       </c>
       <c r="D111" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -2980,7 +2980,7 @@
         <v>9</v>
       </c>
       <c r="G111" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112">
@@ -2992,7 +2992,7 @@
         <v>116</v>
       </c>
       <c r="D112" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -3001,7 +3001,7 @@
         <v>9</v>
       </c>
       <c r="G112" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113">
@@ -3013,7 +3013,7 @@
         <v>116</v>
       </c>
       <c r="D113" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -3022,7 +3022,7 @@
         <v>9</v>
       </c>
       <c r="G113" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114">
@@ -3036,7 +3036,7 @@
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E114" t="s">
         <v>12</v>
@@ -3045,7 +3045,7 @@
         <v>13</v>
       </c>
       <c r="G114" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115">
@@ -3057,7 +3057,7 @@
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E115" t="s">
         <v>12</v>
@@ -3066,7 +3066,7 @@
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116">
@@ -3078,7 +3078,7 @@
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E116" t="s">
         <v>12</v>
@@ -3087,7 +3087,7 @@
         <v>13</v>
       </c>
       <c r="G116" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
@@ -3099,7 +3099,7 @@
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E117" t="s">
         <v>12</v>
@@ -3108,7 +3108,7 @@
         <v>13</v>
       </c>
       <c r="G117" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118">
@@ -3120,7 +3120,7 @@
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E118" t="s">
         <v>12</v>
@@ -3129,7 +3129,7 @@
         <v>13</v>
       </c>
       <c r="G118" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119">
@@ -3141,7 +3141,7 @@
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E119" t="s">
         <v>12</v>
@@ -3150,7 +3150,7 @@
         <v>13</v>
       </c>
       <c r="G119" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120">
@@ -3162,7 +3162,7 @@
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E120" t="s">
         <v>12</v>
@@ -3171,7 +3171,7 @@
         <v>13</v>
       </c>
       <c r="G120" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121">
@@ -3183,7 +3183,7 @@
         <v>116</v>
       </c>
       <c r="D121" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -3192,7 +3192,7 @@
         <v>9</v>
       </c>
       <c r="G121" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122">
@@ -3204,7 +3204,7 @@
         <v>116</v>
       </c>
       <c r="D122" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -3213,7 +3213,7 @@
         <v>9</v>
       </c>
       <c r="G122" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123">
@@ -3225,7 +3225,7 @@
         <v>116</v>
       </c>
       <c r="D123" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -3234,7 +3234,7 @@
         <v>9</v>
       </c>
       <c r="G123" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124">
@@ -3246,7 +3246,7 @@
         <v>116</v>
       </c>
       <c r="D124" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9</v>
       </c>
       <c r="G124" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125">
@@ -3267,7 +3267,7 @@
         <v>116</v>
       </c>
       <c r="D125" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -3276,7 +3276,7 @@
         <v>9</v>
       </c>
       <c r="G125" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126">
@@ -3288,7 +3288,7 @@
         <v>116</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -3297,7 +3297,7 @@
         <v>9</v>
       </c>
       <c r="G126" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
@@ -3309,7 +3309,7 @@
         <v>116</v>
       </c>
       <c r="D127" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -3318,7 +3318,7 @@
         <v>9</v>
       </c>
       <c r="G127" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128">
@@ -3924,7 +3924,7 @@
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E156" t="s">
         <v>12</v>
@@ -3933,7 +3933,7 @@
         <v>13</v>
       </c>
       <c r="G156" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157">
@@ -3945,7 +3945,7 @@
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E157" t="s">
         <v>12</v>
@@ -3954,7 +3954,7 @@
         <v>13</v>
       </c>
       <c r="G157" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="158">
@@ -3966,7 +3966,7 @@
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E158" t="s">
         <v>12</v>
@@ -3975,7 +3975,7 @@
         <v>13</v>
       </c>
       <c r="G158" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="159">
@@ -3987,7 +3987,7 @@
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E159" t="s">
         <v>12</v>
@@ -3996,7 +3996,7 @@
         <v>13</v>
       </c>
       <c r="G159" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="160">
@@ -4008,7 +4008,7 @@
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E160" t="s">
         <v>12</v>
@@ -4017,7 +4017,7 @@
         <v>13</v>
       </c>
       <c r="G160" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161">
@@ -4029,7 +4029,7 @@
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E161" t="s">
         <v>12</v>
@@ -4038,7 +4038,7 @@
         <v>13</v>
       </c>
       <c r="G161" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="162">
@@ -4050,7 +4050,7 @@
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E162" t="s">
         <v>12</v>
@@ -4059,7 +4059,7 @@
         <v>13</v>
       </c>
       <c r="G162" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="163">
@@ -4071,7 +4071,7 @@
         <v>116</v>
       </c>
       <c r="D163" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -4080,7 +4080,7 @@
         <v>9</v>
       </c>
       <c r="G163" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164">
@@ -4092,7 +4092,7 @@
         <v>116</v>
       </c>
       <c r="D164" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -4101,7 +4101,7 @@
         <v>9</v>
       </c>
       <c r="G164" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="165">
@@ -4113,7 +4113,7 @@
         <v>116</v>
       </c>
       <c r="D165" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -4122,7 +4122,7 @@
         <v>9</v>
       </c>
       <c r="G165" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166">
@@ -4134,7 +4134,7 @@
         <v>116</v>
       </c>
       <c r="D166" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -4143,7 +4143,7 @@
         <v>9</v>
       </c>
       <c r="G166" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167">
@@ -4155,7 +4155,7 @@
         <v>116</v>
       </c>
       <c r="D167" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -4164,7 +4164,7 @@
         <v>9</v>
       </c>
       <c r="G167" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168">
@@ -4176,7 +4176,7 @@
         <v>116</v>
       </c>
       <c r="D168" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -4185,7 +4185,7 @@
         <v>9</v>
       </c>
       <c r="G168" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169">
@@ -4197,7 +4197,7 @@
         <v>116</v>
       </c>
       <c r="D169" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -4206,7 +4206,7 @@
         <v>9</v>
       </c>
       <c r="G169" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170">
@@ -4812,7 +4812,7 @@
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E198" t="s">
         <v>12</v>
@@ -4821,7 +4821,7 @@
         <v>13</v>
       </c>
       <c r="G198" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199">
@@ -4833,7 +4833,7 @@
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E199" t="s">
         <v>12</v>
@@ -4842,7 +4842,7 @@
         <v>13</v>
       </c>
       <c r="G199" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="200">
@@ -4854,7 +4854,7 @@
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E200" t="s">
         <v>12</v>
@@ -4863,7 +4863,7 @@
         <v>13</v>
       </c>
       <c r="G200" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="201">
@@ -4875,7 +4875,7 @@
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E201" t="s">
         <v>12</v>
@@ -4884,7 +4884,7 @@
         <v>13</v>
       </c>
       <c r="G201" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="202">
@@ -4896,7 +4896,7 @@
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E202" t="s">
         <v>12</v>
@@ -4905,7 +4905,7 @@
         <v>13</v>
       </c>
       <c r="G202" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="203">
@@ -4917,7 +4917,7 @@
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E203" t="s">
         <v>12</v>
@@ -4926,7 +4926,7 @@
         <v>13</v>
       </c>
       <c r="G203" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="204">
@@ -4938,7 +4938,7 @@
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E204" t="s">
         <v>12</v>
@@ -4947,7 +4947,7 @@
         <v>13</v>
       </c>
       <c r="G204" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="205">
@@ -4959,7 +4959,7 @@
         <v>116</v>
       </c>
       <c r="D205" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -4968,7 +4968,7 @@
         <v>9</v>
       </c>
       <c r="G205" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206">
@@ -4980,7 +4980,7 @@
         <v>116</v>
       </c>
       <c r="D206" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -4989,7 +4989,7 @@
         <v>9</v>
       </c>
       <c r="G206" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207">
@@ -5001,7 +5001,7 @@
         <v>116</v>
       </c>
       <c r="D207" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -5010,7 +5010,7 @@
         <v>9</v>
       </c>
       <c r="G207" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208">
@@ -5022,7 +5022,7 @@
         <v>116</v>
       </c>
       <c r="D208" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -5031,7 +5031,7 @@
         <v>9</v>
       </c>
       <c r="G208" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209">
@@ -5043,7 +5043,7 @@
         <v>116</v>
       </c>
       <c r="D209" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -5052,7 +5052,7 @@
         <v>9</v>
       </c>
       <c r="G209" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="210">
@@ -5064,7 +5064,7 @@
         <v>116</v>
       </c>
       <c r="D210" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -5073,7 +5073,7 @@
         <v>9</v>
       </c>
       <c r="G210" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211">
@@ -5085,7 +5085,7 @@
         <v>116</v>
       </c>
       <c r="D211" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -5094,7 +5094,7 @@
         <v>9</v>
       </c>
       <c r="G211" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="212">
@@ -5108,7 +5108,7 @@
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E212" t="s">
         <v>12</v>
@@ -5117,7 +5117,7 @@
         <v>13</v>
       </c>
       <c r="G212" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="213">
@@ -5129,7 +5129,7 @@
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E213" t="s">
         <v>12</v>
@@ -5138,7 +5138,7 @@
         <v>13</v>
       </c>
       <c r="G213" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="214">
@@ -5150,7 +5150,7 @@
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E214" t="s">
         <v>12</v>
@@ -5159,7 +5159,7 @@
         <v>13</v>
       </c>
       <c r="G214" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="215">
@@ -5171,7 +5171,7 @@
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E215" t="s">
         <v>12</v>
@@ -5180,7 +5180,7 @@
         <v>13</v>
       </c>
       <c r="G215" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="216">
@@ -5192,7 +5192,7 @@
         <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E216" t="s">
         <v>12</v>
@@ -5201,7 +5201,7 @@
         <v>13</v>
       </c>
       <c r="G216" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="217">
@@ -5213,7 +5213,7 @@
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E217" t="s">
         <v>12</v>
@@ -5222,7 +5222,7 @@
         <v>13</v>
       </c>
       <c r="G217" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="218">
@@ -5234,7 +5234,7 @@
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E218" t="s">
         <v>12</v>
@@ -5243,7 +5243,7 @@
         <v>13</v>
       </c>
       <c r="G218" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="219">
@@ -5255,7 +5255,7 @@
         <v>116</v>
       </c>
       <c r="D219" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -5264,7 +5264,7 @@
         <v>9</v>
       </c>
       <c r="G219" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220">
@@ -5276,7 +5276,7 @@
         <v>116</v>
       </c>
       <c r="D220" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -5285,7 +5285,7 @@
         <v>9</v>
       </c>
       <c r="G220" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221">
@@ -5297,7 +5297,7 @@
         <v>116</v>
       </c>
       <c r="D221" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -5306,7 +5306,7 @@
         <v>9</v>
       </c>
       <c r="G221" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222">
@@ -5318,7 +5318,7 @@
         <v>116</v>
       </c>
       <c r="D222" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -5327,7 +5327,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="223">
@@ -5339,7 +5339,7 @@
         <v>116</v>
       </c>
       <c r="D223" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -5348,7 +5348,7 @@
         <v>9</v>
       </c>
       <c r="G223" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="224">
@@ -5360,7 +5360,7 @@
         <v>116</v>
       </c>
       <c r="D224" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -5369,7 +5369,7 @@
         <v>9</v>
       </c>
       <c r="G224" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="225">
@@ -5381,7 +5381,7 @@
         <v>116</v>
       </c>
       <c r="D225" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -5390,26 +5390,28 @@
         <v>9</v>
       </c>
       <c r="G225" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="A16:A29"/>
+    <mergeCell ref="A30:A43"/>
+    <mergeCell ref="A44:A57"/>
+    <mergeCell ref="A58:A71"/>
+    <mergeCell ref="A72:A85"/>
+    <mergeCell ref="A86:A99"/>
+    <mergeCell ref="A100:A113"/>
+    <mergeCell ref="A114:A127"/>
+    <mergeCell ref="A128:A141"/>
+    <mergeCell ref="A142:A155"/>
+    <mergeCell ref="A156:A169"/>
+    <mergeCell ref="A170:A183"/>
+    <mergeCell ref="A184:A197"/>
+    <mergeCell ref="A198:A211"/>
+    <mergeCell ref="A212:A225"/>
+  </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="4294967295" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
